--- a/validaciones_Y_ChecklistDeRequerimeintos/CheckList_Estatus-001-V.1.4.xlsx
+++ b/validaciones_Y_ChecklistDeRequerimeintos/CheckList_Estatus-001-V.1.4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ITZELPROYECTO\MEDICAL_ISOR_INTEGRADORA_REPO_NUEVO\integradoraTeampoderoso\validaciones_Y_ChecklistDeRequerimeintos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E7EEA2-9BA5-4856-9408-4F8E9F4CB356}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0437C1-D673-4B1B-B404-5C7A8AF425B9}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="586" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DEFECTOS!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DEFECTOS!$A$1:$M$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="64">
   <si>
     <t>Descripción</t>
   </si>
@@ -734,6 +734,66 @@
       <t xml:space="preserve"> Al mismo tiempo tambíen se esta guardando el numero de telefono, ya que si cerramos el modal de detalle de cita y queremos agendar una nueva, el campo de telefono se encuentra con el numero de telefono a la vista </t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Incidencia: Modulo citas </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica"/>
+      </rPr>
+      <t xml:space="preserve">
+Rol: Admin
+Descripción:  Cambiar modulo citas, ahora va estar en la pagina principal</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Incidencia: Modulo editar cita</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica"/>
+      </rPr>
+      <t xml:space="preserve">
+Rol: Admin
+Descripción:  Al editar una cita , solo debe estar habilitado el tipo de servicio y el estatus. Ademas de acomodar el tamaño del modal para que no se vea tan grande</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Incidencia: Modulo editar cita</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica"/>
+      </rPr>
+      <t xml:space="preserve">
+Rol: Admin
+Descripción:  Modificar iconos, quitar boton de agregar comentario</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Incidencia: Modulo guardar cita</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica"/>
+      </rPr>
+      <t xml:space="preserve">
+Rol: Usuario
+Descripción:  Al dar clic en aceptar agendar cita , la pantalla se queda cargando , se envia mensaje y todo pero el detalle de cita no llega</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1215,7 +1275,199 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="91">
+  <dxfs count="99">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1468,76 +1720,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1769,17 +1951,6 @@
       <fill>
         <patternFill>
           <fgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3075,6 +3246,182 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676413</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>939211</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3823805</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>2776623</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Imagen 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D2E55CF-CEE0-4606-8507-6AC9E272D614}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1670326" y="19133341"/>
+          <a:ext cx="3147392" cy="1837412"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>662609</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>869673</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3989457</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>3521845</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Imagen 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1249F3B9-6CCA-4376-B00A-C6D07973F9B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1656522" y="22804782"/>
+          <a:ext cx="3326848" cy="2652172"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1366631</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1352826</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5310531</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>2762723</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Imagen 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EEAD774-2246-47A8-873F-66BC400FCAAE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2360544" y="27028913"/>
+          <a:ext cx="3943900" cy="1409897"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>786847</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>1145761</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4941956</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>3294956</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Imagen 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30CC997D-5231-46C8-90AC-1524DECEC1B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1780760" y="30562826"/>
+          <a:ext cx="4155109" cy="2149195"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3416,6 +3763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:ATS2372"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
@@ -3475,7 +3823,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:1215" s="26" customFormat="1" ht="207.6" customHeight="1">
+    <row r="2" spans="1:1215" s="26" customFormat="1" ht="207.6" hidden="1" customHeight="1">
       <c r="A2" s="28" t="s">
         <v>30</v>
       </c>
@@ -4710,7 +5058,7 @@
       <c r="ATR2"/>
       <c r="ATS2"/>
     </row>
-    <row r="3" spans="1:1215" ht="256.89999999999998" customHeight="1">
+    <row r="3" spans="1:1215" ht="256.89999999999998" hidden="1" customHeight="1">
       <c r="A3" s="28" t="s">
         <v>31</v>
       </c>
@@ -4933,7 +5281,7 @@
       <c r="HB3" s="17"/>
       <c r="HC3" s="17"/>
     </row>
-    <row r="4" spans="1:1215" ht="217.15" customHeight="1">
+    <row r="4" spans="1:1215" ht="217.15" hidden="1" customHeight="1">
       <c r="A4" s="28" t="s">
         <v>32</v>
       </c>
@@ -5156,7 +5504,7 @@
       <c r="HB4" s="17"/>
       <c r="HC4" s="17"/>
     </row>
-    <row r="5" spans="1:1215" ht="277.14999999999998" customHeight="1">
+    <row r="5" spans="1:1215" ht="277.14999999999998" hidden="1" customHeight="1">
       <c r="A5" s="28" t="s">
         <v>33</v>
       </c>
@@ -5379,7 +5727,7 @@
       <c r="HB5" s="17"/>
       <c r="HC5" s="17"/>
     </row>
-    <row r="6" spans="1:1215" ht="303" customHeight="1">
+    <row r="6" spans="1:1215" ht="303" hidden="1" customHeight="1">
       <c r="A6" s="28" t="s">
         <v>34</v>
       </c>
@@ -5602,7 +5950,7 @@
       <c r="HB6" s="17"/>
       <c r="HC6" s="17"/>
     </row>
-    <row r="7" spans="1:1215" ht="329.45" customHeight="1">
+    <row r="7" spans="1:1215" ht="329.45" hidden="1" customHeight="1">
       <c r="A7" s="28" t="s">
         <v>35</v>
       </c>
@@ -5827,7 +6175,7 @@
       <c r="HB7" s="17"/>
       <c r="HC7" s="17"/>
     </row>
-    <row r="8" spans="1:1215" ht="327" customHeight="1">
+    <row r="8" spans="1:1215" ht="327" hidden="1" customHeight="1">
       <c r="A8" s="28" t="s">
         <v>36</v>
       </c>
@@ -6271,7 +6619,7 @@
       <c r="HB9" s="17"/>
       <c r="HC9" s="17"/>
     </row>
-    <row r="10" spans="1:1215" ht="211.15" customHeight="1">
+    <row r="10" spans="1:1215" ht="211.15" hidden="1" customHeight="1">
       <c r="A10" s="34"/>
       <c r="B10" s="42" t="s">
         <v>46</v>
@@ -6492,7 +6840,7 @@
       <c r="HB10" s="17"/>
       <c r="HC10" s="17"/>
     </row>
-    <row r="11" spans="1:1215" ht="208.9" customHeight="1">
+    <row r="11" spans="1:1215" ht="208.9" hidden="1" customHeight="1">
       <c r="A11" s="34"/>
       <c r="B11" s="43" t="s">
         <v>47</v>
@@ -6713,7 +7061,7 @@
       <c r="HB11" s="17"/>
       <c r="HC11" s="17"/>
     </row>
-    <row r="12" spans="1:1215" ht="203.45" customHeight="1">
+    <row r="12" spans="1:1215" ht="203.45" hidden="1" customHeight="1">
       <c r="A12" s="34"/>
       <c r="B12" s="42" t="s">
         <v>48</v>
@@ -6934,7 +7282,7 @@
       <c r="HB12" s="17"/>
       <c r="HC12" s="17"/>
     </row>
-    <row r="13" spans="1:1215" ht="341.45" customHeight="1">
+    <row r="13" spans="1:1215" ht="341.45" hidden="1" customHeight="1">
       <c r="A13" s="34"/>
       <c r="B13" s="42" t="s">
         <v>49</v>
@@ -8662,21 +9010,32 @@
       <c r="HB20" s="17"/>
       <c r="HC20" s="17"/>
     </row>
-    <row r="21" spans="1:211">
-      <c r="A21" s="32"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="27"/>
+    <row r="21" spans="1:211" ht="294.75" customHeight="1">
+      <c r="A21" s="34"/>
+      <c r="B21" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="51">
+        <v>45978</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
       <c r="V21" s="17"/>
       <c r="W21" s="17"/>
       <c r="X21" s="17"/>
@@ -8868,21 +9227,32 @@
       <c r="HB21" s="17"/>
       <c r="HC21" s="17"/>
     </row>
-    <row r="22" spans="1:211" ht="39.950000000000003" customHeight="1">
-      <c r="A22" s="32"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="27"/>
+    <row r="22" spans="1:211" ht="294.75" customHeight="1">
+      <c r="A22" s="34"/>
+      <c r="B22" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" s="51">
+        <v>45978</v>
+      </c>
+      <c r="H22" s="11"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="40"/>
       <c r="V22" s="17"/>
       <c r="W22" s="17"/>
       <c r="X22" s="17"/>
@@ -9074,21 +9444,32 @@
       <c r="HB22" s="17"/>
       <c r="HC22" s="17"/>
     </row>
-    <row r="23" spans="1:211" ht="30" customHeight="1">
-      <c r="A23" s="32"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
+    <row r="23" spans="1:211" ht="294.75" customHeight="1">
+      <c r="A23" s="34"/>
+      <c r="B23" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" s="51">
+        <v>45978</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="40"/>
+      <c r="M23" s="40"/>
       <c r="V23" s="17"/>
       <c r="W23" s="17"/>
       <c r="X23" s="17"/>
@@ -9280,21 +9661,222 @@
       <c r="HB23" s="17"/>
       <c r="HC23" s="17"/>
     </row>
-    <row r="24" spans="1:211" ht="15" customHeight="1">
-      <c r="A24" s="32"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27"/>
+    <row r="24" spans="1:211" ht="294.75" customHeight="1">
+      <c r="A24" s="34"/>
+      <c r="B24" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="51">
+        <v>45979</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40"/>
+      <c r="V24" s="17"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="17"/>
+      <c r="Y24" s="17"/>
+      <c r="Z24" s="17"/>
+      <c r="AA24" s="17"/>
+      <c r="AB24" s="17"/>
+      <c r="AC24" s="17"/>
+      <c r="AD24" s="17"/>
+      <c r="AE24" s="17"/>
+      <c r="AF24" s="17"/>
+      <c r="AG24" s="17"/>
+      <c r="AH24" s="17"/>
+      <c r="AI24" s="17"/>
+      <c r="AJ24" s="17"/>
+      <c r="AK24" s="17"/>
+      <c r="AL24" s="17"/>
+      <c r="AM24" s="17"/>
+      <c r="AN24" s="17"/>
+      <c r="AO24" s="17"/>
+      <c r="AP24" s="17"/>
+      <c r="AQ24" s="17"/>
+      <c r="AR24" s="17"/>
+      <c r="AS24" s="17"/>
+      <c r="AT24" s="17"/>
+      <c r="AU24" s="17"/>
+      <c r="AV24" s="17"/>
+      <c r="AW24" s="17"/>
+      <c r="AX24" s="17"/>
+      <c r="AY24" s="17"/>
+      <c r="AZ24" s="17"/>
+      <c r="BA24" s="17"/>
+      <c r="BB24" s="17"/>
+      <c r="BC24" s="17"/>
+      <c r="BD24" s="17"/>
+      <c r="BE24" s="17"/>
+      <c r="BF24" s="17"/>
+      <c r="BG24" s="17"/>
+      <c r="BH24" s="17"/>
+      <c r="BI24" s="17"/>
+      <c r="BJ24" s="17"/>
+      <c r="BK24" s="17"/>
+      <c r="BL24" s="17"/>
+      <c r="BM24" s="17"/>
+      <c r="BN24" s="17"/>
+      <c r="BO24" s="17"/>
+      <c r="BP24" s="17"/>
+      <c r="BQ24" s="17"/>
+      <c r="BR24" s="17"/>
+      <c r="BS24" s="17"/>
+      <c r="BT24" s="17"/>
+      <c r="BU24" s="17"/>
+      <c r="BV24" s="17"/>
+      <c r="BW24" s="17"/>
+      <c r="BX24" s="17"/>
+      <c r="BY24" s="17"/>
+      <c r="BZ24" s="17"/>
+      <c r="CA24" s="17"/>
+      <c r="CB24" s="17"/>
+      <c r="CC24" s="17"/>
+      <c r="CD24" s="17"/>
+      <c r="CE24" s="17"/>
+      <c r="CF24" s="17"/>
+      <c r="CG24" s="17"/>
+      <c r="CH24" s="17"/>
+      <c r="CI24" s="17"/>
+      <c r="CJ24" s="17"/>
+      <c r="CK24" s="17"/>
+      <c r="CL24" s="17"/>
+      <c r="CM24" s="17"/>
+      <c r="CN24" s="17"/>
+      <c r="CO24" s="17"/>
+      <c r="CP24" s="17"/>
+      <c r="CQ24" s="17"/>
+      <c r="CR24" s="17"/>
+      <c r="CS24" s="17"/>
+      <c r="CT24" s="17"/>
+      <c r="CU24" s="17"/>
+      <c r="CV24" s="17"/>
+      <c r="CW24" s="17"/>
+      <c r="CX24" s="17"/>
+      <c r="CY24" s="17"/>
+      <c r="CZ24" s="17"/>
+      <c r="DA24" s="17"/>
+      <c r="DB24" s="17"/>
+      <c r="DC24" s="17"/>
+      <c r="DD24" s="17"/>
+      <c r="DE24" s="17"/>
+      <c r="DF24" s="17"/>
+      <c r="DG24" s="17"/>
+      <c r="DH24" s="17"/>
+      <c r="DI24" s="17"/>
+      <c r="DJ24" s="17"/>
+      <c r="DK24" s="17"/>
+      <c r="DL24" s="17"/>
+      <c r="DM24" s="17"/>
+      <c r="DN24" s="17"/>
+      <c r="DO24" s="17"/>
+      <c r="DP24" s="17"/>
+      <c r="DQ24" s="17"/>
+      <c r="DR24" s="17"/>
+      <c r="DS24" s="17"/>
+      <c r="DT24" s="17"/>
+      <c r="DU24" s="17"/>
+      <c r="DV24" s="17"/>
+      <c r="DW24" s="17"/>
+      <c r="DX24" s="17"/>
+      <c r="DY24" s="17"/>
+      <c r="DZ24" s="17"/>
+      <c r="EA24" s="17"/>
+      <c r="EB24" s="17"/>
+      <c r="EC24" s="17"/>
+      <c r="ED24" s="17"/>
+      <c r="EE24" s="17"/>
+      <c r="EF24" s="17"/>
+      <c r="EG24" s="17"/>
+      <c r="EH24" s="17"/>
+      <c r="EI24" s="17"/>
+      <c r="EJ24" s="17"/>
+      <c r="EK24" s="17"/>
+      <c r="EL24" s="17"/>
+      <c r="EM24" s="17"/>
+      <c r="EN24" s="17"/>
+      <c r="EO24" s="17"/>
+      <c r="EP24" s="17"/>
+      <c r="EQ24" s="17"/>
+      <c r="ER24" s="17"/>
+      <c r="ES24" s="17"/>
+      <c r="ET24" s="17"/>
+      <c r="EU24" s="17"/>
+      <c r="EV24" s="17"/>
+      <c r="EW24" s="17"/>
+      <c r="EX24" s="17"/>
+      <c r="EY24" s="17"/>
+      <c r="EZ24" s="17"/>
+      <c r="FA24" s="17"/>
+      <c r="FB24" s="17"/>
+      <c r="FC24" s="17"/>
+      <c r="FD24" s="17"/>
+      <c r="FE24" s="17"/>
+      <c r="FF24" s="17"/>
+      <c r="FG24" s="17"/>
+      <c r="FH24" s="17"/>
+      <c r="FI24" s="17"/>
+      <c r="FJ24" s="17"/>
+      <c r="FK24" s="17"/>
+      <c r="FL24" s="17"/>
+      <c r="FM24" s="17"/>
+      <c r="FN24" s="17"/>
+      <c r="FO24" s="17"/>
+      <c r="FP24" s="17"/>
+      <c r="FQ24" s="17"/>
+      <c r="FR24" s="17"/>
+      <c r="FS24" s="17"/>
+      <c r="FT24" s="17"/>
+      <c r="FU24" s="17"/>
+      <c r="FV24" s="17"/>
+      <c r="FW24" s="17"/>
+      <c r="FX24" s="17"/>
+      <c r="FY24" s="17"/>
+      <c r="FZ24" s="17"/>
+      <c r="GA24" s="17"/>
+      <c r="GB24" s="17"/>
+      <c r="GC24" s="17"/>
+      <c r="GD24" s="17"/>
+      <c r="GE24" s="17"/>
+      <c r="GF24" s="17"/>
+      <c r="GG24" s="17"/>
+      <c r="GH24" s="17"/>
+      <c r="GI24" s="17"/>
+      <c r="GJ24" s="17"/>
+      <c r="GK24" s="17"/>
+      <c r="GL24" s="17"/>
+      <c r="GM24" s="17"/>
+      <c r="GN24" s="17"/>
+      <c r="GO24" s="17"/>
+      <c r="GP24" s="17"/>
+      <c r="GQ24" s="17"/>
+      <c r="GR24" s="17"/>
+      <c r="GS24" s="17"/>
+      <c r="GT24" s="17"/>
+      <c r="GU24" s="17"/>
+      <c r="GV24" s="17"/>
+      <c r="GW24" s="17"/>
+      <c r="GX24" s="17"/>
+      <c r="GY24" s="17"/>
+      <c r="GZ24" s="17"/>
+      <c r="HA24" s="17"/>
+      <c r="HB24" s="17"/>
+      <c r="HC24" s="17"/>
     </row>
     <row r="25" spans="1:211" ht="15" customHeight="1">
       <c r="A25" s="32"/>
@@ -16987,325 +17569,403 @@
       <c r="B2372" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M17" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:M20" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="ABIERTO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="containsText" dxfId="90" priority="642" operator="containsText" text="EN PROGRESO">
+    <cfRule type="containsText" dxfId="98" priority="658" operator="containsText" text="EN PROGRESO">
       <formula>NOT(ISERROR(SEARCH("EN PROGRESO",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="89" priority="645" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="97" priority="661" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",A1)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="651" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="667" stopIfTrue="1" operator="equal">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="650" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="666" stopIfTrue="1" operator="equal">
       <formula>"CLOSED"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="649" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="665" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="648" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="93" priority="664" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="641" operator="containsText" text="EN PROGRESO">
+    <cfRule type="containsText" dxfId="92" priority="657" operator="containsText" text="EN PROGRESO">
       <formula>NOT(ISERROR(SEARCH("EN PROGRESO",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="83" priority="647" operator="containsText" text="CERRADO">
+    <cfRule type="containsText" dxfId="91" priority="663" operator="containsText" text="CERRADO">
       <formula>NOT(ISERROR(SEARCH("CERRADO",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="82" priority="643" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="90" priority="659" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="81" priority="644" operator="containsText" text="CERRADO">
+    <cfRule type="containsText" dxfId="89" priority="660" operator="containsText" text="CERRADO">
       <formula>NOT(ISERROR(SEARCH("CERRADO",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1 D1">
-    <cfRule type="containsText" dxfId="80" priority="646" operator="containsText" text="CERRADO">
+    <cfRule type="containsText" dxfId="88" priority="662" operator="containsText" text="CERRADO">
       <formula>NOT(ISERROR(SEARCH("CERRADO",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="containsText" dxfId="79" priority="294" operator="containsText" text="PENDIENTE">
+    <cfRule type="containsText" dxfId="87" priority="310" operator="containsText" text="PENDIENTE">
       <formula>NOT(ISERROR(SEARCH("PENDIENTE",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="cellIs" dxfId="78" priority="1682" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="1698" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="77" priority="1681" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="85" priority="1697" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="1680" operator="containsText" text="CERRADO">
+    <cfRule type="containsText" dxfId="84" priority="1696" operator="containsText" text="CERRADO">
       <formula>NOT(ISERROR(SEARCH("CERRADO",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="1679" operator="containsText" text="CERRADO">
+    <cfRule type="containsText" dxfId="83" priority="1695" operator="containsText" text="CERRADO">
       <formula>NOT(ISERROR(SEARCH("CERRADO",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="74" priority="1678" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="82" priority="1694" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="73" priority="1675" operator="containsText" text="EN PROGRESO">
+    <cfRule type="containsText" dxfId="81" priority="1691" operator="containsText" text="EN PROGRESO">
       <formula>NOT(ISERROR(SEARCH("EN PROGRESO",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="1677" operator="containsText" text="CERRADO">
+    <cfRule type="containsText" dxfId="80" priority="1693" operator="containsText" text="CERRADO">
       <formula>NOT(ISERROR(SEARCH("CERRADO",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="71" priority="1676" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="79" priority="1692" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="70" priority="1674" operator="containsText" text="EN PROGRESO">
+    <cfRule type="containsText" dxfId="78" priority="1690" operator="containsText" text="EN PROGRESO">
       <formula>NOT(ISERROR(SEARCH("EN PROGRESO",B1)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="1683" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="1699" stopIfTrue="1" operator="equal">
       <formula>"CLOSED"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="1684" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="1700" stopIfTrue="1" operator="equal">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="containsText" dxfId="67" priority="270" operator="containsText" text="SHOWSTOPPER">
+    <cfRule type="containsText" dxfId="75" priority="286" operator="containsText" text="SHOWSTOPPER">
       <formula>NOT(ISERROR(SEARCH("SHOWSTOPPER",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="273" operator="containsText" text="ALTO">
+    <cfRule type="containsText" dxfId="74" priority="289" operator="containsText" text="ALTO">
       <formula>NOT(ISERROR(SEARCH("ALTO",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="65" priority="272" operator="containsText" text="MEDIO">
+    <cfRule type="containsText" dxfId="73" priority="288" operator="containsText" text="MEDIO">
       <formula>NOT(ISERROR(SEARCH("MEDIO",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="271" operator="containsText" text="show">
+    <cfRule type="containsText" dxfId="72" priority="287" operator="containsText" text="show">
       <formula>NOT(ISERROR(SEARCH("show",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="containsText" dxfId="63" priority="1782" operator="containsText" text="ALTO">
+    <cfRule type="containsText" dxfId="71" priority="1798" operator="containsText" text="ALTO">
       <formula>NOT(ISERROR(SEARCH("ALTO",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="1783" operator="containsText" text="Showstopper ">
+    <cfRule type="containsText" dxfId="70" priority="1799" operator="containsText" text="Showstopper ">
       <formula>NOT(ISERROR(SEARCH("Showstopper ",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="61" priority="1787" operator="containsText" text="ALTO">
+    <cfRule type="containsText" dxfId="69" priority="1803" operator="containsText" text="ALTO">
       <formula>NOT(ISERROR(SEARCH("ALTO",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="1788" operator="containsText" text="ALTO">
+    <cfRule type="containsText" dxfId="68" priority="1804" operator="containsText" text="ALTO">
       <formula>NOT(ISERROR(SEARCH("ALTO",C1)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="1789" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="1805" stopIfTrue="1" operator="equal">
       <formula>"Medio"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="1790" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="1806" stopIfTrue="1" operator="equal">
       <formula>"Bajo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="1791" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="1807" stopIfTrue="1" operator="equal">
       <formula>"Alto"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="56" priority="21" operator="containsText" text="ALTO">
+    <cfRule type="containsText" dxfId="64" priority="37" operator="containsText" text="ALTO">
       <formula>NOT(ISERROR(SEARCH("ALTO",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15">
-    <cfRule type="containsText" dxfId="55" priority="23" operator="containsText" text="MEDIO">
+    <cfRule type="containsText" dxfId="63" priority="39" operator="containsText" text="MEDIO">
       <formula>NOT(ISERROR(SEARCH("MEDIO",C2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="25" operator="containsText" text="BAJA">
+    <cfRule type="containsText" dxfId="62" priority="41" operator="containsText" text="BAJA">
       <formula>NOT(ISERROR(SEARCH("BAJA",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:C15">
-    <cfRule type="containsText" dxfId="53" priority="22" operator="containsText" text="ALTO">
+    <cfRule type="containsText" dxfId="61" priority="38" operator="containsText" text="ALTO">
       <formula>NOT(ISERROR(SEARCH("ALTO",C5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="containsText" dxfId="52" priority="268" operator="containsText" text="BAJA">
+    <cfRule type="containsText" dxfId="60" priority="284" operator="containsText" text="BAJA">
       <formula>NOT(ISERROR(SEARCH("BAJA",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C51:C1048576">
-    <cfRule type="containsText" dxfId="50" priority="1221" operator="containsText" text="SHOWSTOPPER">
+    <cfRule type="containsText" dxfId="59" priority="1237" operator="containsText" text="SHOWSTOPPER">
       <formula>NOT(ISERROR(SEARCH("SHOWSTOPPER",C51)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="1219" operator="containsText" text="BAJA">
+    <cfRule type="containsText" dxfId="58" priority="1235" operator="containsText" text="BAJA">
       <formula>NOT(ISERROR(SEARCH("BAJA",C51)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="1222" operator="containsText" text="show">
+    <cfRule type="containsText" dxfId="57" priority="1238" operator="containsText" text="show">
       <formula>NOT(ISERROR(SEARCH("show",C51)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="47" priority="1223" operator="containsText" text="MEDIO">
+    <cfRule type="containsText" dxfId="56" priority="1239" operator="containsText" text="MEDIO">
       <formula>NOT(ISERROR(SEARCH("MEDIO",C51)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="1224" operator="containsText" text="ALTO">
+    <cfRule type="containsText" dxfId="55" priority="1240" operator="containsText" text="ALTO">
       <formula>NOT(ISERROR(SEARCH("ALTO",C51)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1 D51:D1048576">
-    <cfRule type="containsText" dxfId="45" priority="127" operator="containsText" text="NO APLICA">
+    <cfRule type="containsText" dxfId="54" priority="143" operator="containsText" text="NO APLICA">
       <formula>NOT(ISERROR(SEARCH("NO APLICA",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1 D51:D1048576">
-    <cfRule type="containsText" dxfId="44" priority="1699" operator="containsText" text="EN PROGRESO">
+    <cfRule type="containsText" dxfId="53" priority="1715" operator="containsText" text="EN PROGRESO">
       <formula>NOT(ISERROR(SEARCH("EN PROGRESO",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="1700" operator="containsText" text="EN PROGRESO">
+    <cfRule type="containsText" dxfId="52" priority="1716" operator="containsText" text="EN PROGRESO">
       <formula>NOT(ISERROR(SEARCH("EN PROGRESO",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="1701" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="51" priority="1717" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="41" priority="1702" operator="containsText" text="CERRADO">
+    <cfRule type="containsText" dxfId="50" priority="1718" operator="containsText" text="CERRADO">
       <formula>NOT(ISERROR(SEARCH("CERRADO",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="containsText" dxfId="40" priority="1665" operator="containsText" text="CERRADO">
+    <cfRule type="containsText" dxfId="49" priority="1681" operator="containsText" text="CERRADO">
       <formula>NOT(ISERROR(SEARCH("CERRADO",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="containsText" dxfId="39" priority="1781" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="48" priority="1797" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="1784" operator="containsText" text="CERRADO">
+    <cfRule type="containsText" dxfId="47" priority="1800" operator="containsText" text="CERRADO">
       <formula>NOT(ISERROR(SEARCH("CERRADO",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="1785" operator="containsText" text="CERRADO">
+    <cfRule type="containsText" dxfId="46" priority="1801" operator="containsText" text="CERRADO">
       <formula>NOT(ISERROR(SEARCH("CERRADO",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="1786" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="45" priority="1802" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",D1)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="1792" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="1808" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="1793" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1809" stopIfTrue="1" operator="equal">
       <formula>"CLOSED"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="1794" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="1810" stopIfTrue="1" operator="equal">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D15">
-    <cfRule type="containsText" dxfId="32" priority="24" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="41" priority="40" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",D2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:D1048576 D1">
-    <cfRule type="containsText" dxfId="31" priority="135" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="40" priority="151" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:D1048576">
-    <cfRule type="containsText" dxfId="30" priority="132" operator="containsText" text="CERRADO">
+    <cfRule type="containsText" dxfId="39" priority="148" operator="containsText" text="CERRADO">
       <formula>NOT(ISERROR(SEARCH("CERRADO",D51)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:D1048576">
-    <cfRule type="containsText" dxfId="29" priority="1428" operator="containsText" text="CERRADO">
+    <cfRule type="containsText" dxfId="38" priority="1444" operator="containsText" text="CERRADO">
       <formula>NOT(ISERROR(SEARCH("CERRADO",D51)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="1225" operator="containsText" text="PENDIENTE">
+    <cfRule type="containsText" dxfId="37" priority="1241" operator="containsText" text="PENDIENTE">
       <formula>NOT(ISERROR(SEARCH("PENDIENTE",D51)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="containsText" dxfId="27" priority="1660" operator="containsText" text="PENDIENTE">
+    <cfRule type="containsText" dxfId="36" priority="1676" operator="containsText" text="PENDIENTE">
       <formula>NOT(ISERROR(SEARCH("PENDIENTE",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="containsText" dxfId="19" priority="18" operator="containsText" text="MEDIO">
+    <cfRule type="containsText" dxfId="35" priority="34" operator="containsText" text="MEDIO">
       <formula>NOT(ISERROR(SEARCH("MEDIO",C16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text="BAJA">
+    <cfRule type="containsText" dxfId="34" priority="36" operator="containsText" text="BAJA">
       <formula>NOT(ISERROR(SEARCH("BAJA",C16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="ALTO">
+    <cfRule type="containsText" dxfId="33" priority="33" operator="containsText" text="ALTO">
       <formula>NOT(ISERROR(SEARCH("ALTO",C16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16">
-    <cfRule type="containsText" dxfId="16" priority="19" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="32" priority="35" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",D16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="containsText" dxfId="15" priority="14" operator="containsText" text="MEDIO">
+    <cfRule type="containsText" dxfId="31" priority="30" operator="containsText" text="MEDIO">
       <formula>NOT(ISERROR(SEARCH("MEDIO",C17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="BAJA">
+    <cfRule type="containsText" dxfId="30" priority="32" operator="containsText" text="BAJA">
       <formula>NOT(ISERROR(SEARCH("BAJA",C17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="ALTO">
+    <cfRule type="containsText" dxfId="29" priority="29" operator="containsText" text="ALTO">
       <formula>NOT(ISERROR(SEARCH("ALTO",C17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D17">
-    <cfRule type="containsText" dxfId="12" priority="15" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="28" priority="31" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",D17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="MEDIO">
+    <cfRule type="containsText" dxfId="27" priority="26" operator="containsText" text="MEDIO">
       <formula>NOT(ISERROR(SEARCH("MEDIO",C18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="BAJA">
+    <cfRule type="containsText" dxfId="26" priority="28" operator="containsText" text="BAJA">
       <formula>NOT(ISERROR(SEARCH("BAJA",C18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="ALTO">
+    <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text="ALTO">
       <formula>NOT(ISERROR(SEARCH("ALTO",C18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18">
-    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="24" priority="27" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",D18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19">
-    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="MEDIO">
+    <cfRule type="containsText" dxfId="23" priority="22" operator="containsText" text="MEDIO">
       <formula>NOT(ISERROR(SEARCH("MEDIO",C19)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="BAJA">
+    <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text="BAJA">
       <formula>NOT(ISERROR(SEARCH("BAJA",C19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="ALTO">
+    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="ALTO">
       <formula>NOT(ISERROR(SEARCH("ALTO",C19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19">
-    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="ABIERTO">
+    <cfRule type="containsText" dxfId="20" priority="23" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",D19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="MEDIO">
+    <cfRule type="containsText" dxfId="19" priority="18" operator="containsText" text="MEDIO">
       <formula>NOT(ISERROR(SEARCH("MEDIO",C20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="BAJA">
+    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text="BAJA">
       <formula>NOT(ISERROR(SEARCH("BAJA",C20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="ALTO">
+    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="ALTO">
       <formula>NOT(ISERROR(SEARCH("ALTO",C20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D20">
+    <cfRule type="containsText" dxfId="16" priority="19" operator="containsText" text="ABIERTO">
+      <formula>NOT(ISERROR(SEARCH("ABIERTO",D20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21">
+    <cfRule type="containsText" dxfId="15" priority="14" operator="containsText" text="MEDIO">
+      <formula>NOT(ISERROR(SEARCH("MEDIO",C21)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="BAJA">
+      <formula>NOT(ISERROR(SEARCH("BAJA",C21)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="ALTO">
+      <formula>NOT(ISERROR(SEARCH("ALTO",C21)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D21">
+    <cfRule type="containsText" dxfId="12" priority="15" operator="containsText" text="ABIERTO">
+      <formula>NOT(ISERROR(SEARCH("ABIERTO",D21)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C22">
+    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="MEDIO">
+      <formula>NOT(ISERROR(SEARCH("MEDIO",C22)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="BAJA">
+      <formula>NOT(ISERROR(SEARCH("BAJA",C22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C22">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="ALTO">
+      <formula>NOT(ISERROR(SEARCH("ALTO",C22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22">
+    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="ABIERTO">
+      <formula>NOT(ISERROR(SEARCH("ABIERTO",D22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C23">
+    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="MEDIO">
+      <formula>NOT(ISERROR(SEARCH("MEDIO",C23)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="BAJA">
+      <formula>NOT(ISERROR(SEARCH("BAJA",C23)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C23">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="ALTO">
+      <formula>NOT(ISERROR(SEARCH("ALTO",C23)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D23">
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="ABIERTO">
+      <formula>NOT(ISERROR(SEARCH("ABIERTO",D23)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="MEDIO">
+      <formula>NOT(ISERROR(SEARCH("MEDIO",C24)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="BAJA">
+      <formula>NOT(ISERROR(SEARCH("BAJA",C24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="ALTO">
+      <formula>NOT(ISERROR(SEARCH("ALTO",C24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D24">
     <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="ABIERTO">
-      <formula>NOT(ISERROR(SEARCH("ABIERTO",D20)))</formula>
+      <formula>NOT(ISERROR(SEARCH("ABIERTO",D24)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
@@ -17316,10 +17976,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E15" xr:uid="{867234F8-EA3F-4FC2-B2C5-59F37B8B762B}">
       <formula1>"--------, Kevin Hernandez, Levi Mundo, Luis Angel"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C20" xr:uid="{2EFE3990-CB5F-4D93-94A6-FF70142F2125}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C24" xr:uid="{2EFE3990-CB5F-4D93-94A6-FF70142F2125}">
       <formula1>"--------, ALTO, MEDIO, SHOWSTOPPER, BAJA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D20" xr:uid="{7C77CF05-9C90-43D6-9300-03C5452EAA1E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D24" xr:uid="{7C77CF05-9C90-43D6-9300-03C5452EAA1E}">
       <formula1>"--------, EN PROGRESO, CERRADO, EN PRUEBA UAT, NO APLICA, ABIERTO, RE-ABIERTO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17339,13 +17999,13 @@
           <x14:formula1>
             <xm:f>CBS!$E$2:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>E16:E20</xm:sqref>
+          <xm:sqref>E16:E24</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5138E63E-5676-4F28-8587-68581ED8ADA1}">
           <x14:formula1>
             <xm:f>CBS!$D$2:$D$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F16:F20</xm:sqref>
+          <xm:sqref>F16:F24</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
